--- a/File Research/CommonObjDat UW2.xlsx
+++ b/File Research/CommonObjDat UW2.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CCB6496-1332-4EA9-9256-A34ECCCB2DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5E622D5-E378-4FB2-8DBF-11A5792C4CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="20640" windowHeight="13080" xr2:uid="{7ED1FA11-2114-4775-965F-EC4009C3E5C9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{7ED1FA11-2114-4775-965F-EC4009C3E5C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1312,9 +1312,6 @@
     <t>ownerbit 7</t>
   </si>
   <si>
-    <t>Bit 1</t>
-  </si>
-  <si>
     <t>bits 2-5
 some sort of test value for a culling check when the game needs more object space</t>
   </si>
@@ -1413,6 +1410,10 @@
     <t>bits 1-4  culling priority for projectiles
 (checked when object hits the ground, only set when object is a damaging projectile type so this is probability the missile is removed from the world on impact when Rng (0-7) is less thanthe value. Any value of 9 means the projectile is destroyed on impact and cause damage in the tile, 0 means object is not removed on impact.
 If the mobile object has bits 4,5,6 at offset 0xA set to 1 the projectile will be removed regardless of the below value and a splash spawned</t>
+  </si>
+  <si>
+    <t>Bit 1
+Likely related to collisons. These are all objects you can stand on??</t>
   </si>
 </sst>
 </file>
@@ -2026,7 +2027,7 @@
         <v>390</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>390</v>
@@ -2039,56 +2040,56 @@
       </c>
       <c r="H2" s="14"/>
       <c r="I2" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>431</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>432</v>
       </c>
       <c r="M2" s="9" t="s">
         <v>383</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="R2" s="5" t="s">
-        <v>425</v>
+        <v>427</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>451</v>
       </c>
       <c r="S2" s="14" t="s">
         <v>384</v>
       </c>
       <c r="T2" s="14"/>
       <c r="U2" s="5" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="V2" s="9" t="s">
         <v>385</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="X2" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="Y2" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Z2" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="AA2" s="6" t="s">
         <v>423</v>
@@ -2098,49 +2099,49 @@
         <v>424</v>
       </c>
       <c r="AD2" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AE2" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AF2" s="9" t="s">
         <v>386</v>
       </c>
       <c r="AG2" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="AH2" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="AI2" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="AJ2" s="6" t="s">
         <v>439</v>
       </c>
-      <c r="AH2" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="AI2" s="6" t="s">
-        <v>437</v>
-      </c>
-      <c r="AJ2" s="6" t="s">
-        <v>440</v>
-      </c>
       <c r="AK2" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AL2" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AM2" s="9" t="s">
         <v>387</v>
       </c>
       <c r="AN2" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AO2" s="6" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AP2" s="9" t="s">
         <v>388</v>
       </c>
       <c r="AQ2" s="12" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="AR2" s="12" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
